--- a/almarazflores_Ex3A_tables.xlsx
+++ b/almarazflores_Ex3A_tables.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\julissaalmarazflores\Documents\DATA_labs\W2_Workshop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4FEF8BC-8A8E-42D0-B2F7-E7CB4A44CAAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC70A462-A178-455D-8195-8FB57A508113}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="18">
   <si>
     <t>ClientID</t>
   </si>
@@ -43,9 +43,6 @@
     <t>Phone</t>
   </si>
   <si>
-    <t>Email</t>
-  </si>
-  <si>
     <t>Address</t>
   </si>
   <si>
@@ -82,10 +79,10 @@
     <t>Amount</t>
   </si>
   <si>
-    <t>Method</t>
-  </si>
-  <si>
     <t>WalkDogID</t>
+  </si>
+  <si>
+    <t>Payment Method</t>
   </si>
 </sst>
 </file>
@@ -433,16 +430,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="10.08984375" customWidth="1"/>
     <col min="3" max="3" width="9.54296875" customWidth="1"/>
     <col min="4" max="4" width="9.90625" customWidth="1"/>
-    <col min="5" max="5" width="9.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -457,9 +453,6 @@
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -474,16 +467,16 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>8</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>9</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>0</v>
@@ -501,19 +494,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -531,22 +524,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -564,13 +557,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/almarazflores_Ex3A_tables.xlsx
+++ b/almarazflores_Ex3A_tables.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\julissaalmarazflores\Documents\DATA_labs\W2_Workshop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC70A462-A178-455D-8195-8FB57A508113}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A58FD1DB-F8A5-4FA2-ABB3-1839C14247A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Clients" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="28">
   <si>
     <t>ClientID</t>
   </si>
@@ -83,12 +83,46 @@
   </si>
   <si>
     <t>Payment Method</t>
+  </si>
+  <si>
+    <t>Complete</t>
+  </si>
+  <si>
+    <t>Card</t>
+  </si>
+  <si>
+    <t>9:00am</t>
+  </si>
+  <si>
+    <t>Buddy</t>
+  </si>
+  <si>
+    <t>Golden Retriever</t>
+  </si>
+  <si>
+    <t>Friendly and Calm</t>
+  </si>
+  <si>
+    <t>Emily</t>
+  </si>
+  <si>
+    <t>Johnson</t>
+  </si>
+  <si>
+    <t>312-555-0184</t>
+  </si>
+  <si>
+    <t>1452 W Lake St, Chicago, IL</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
+    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -144,12 +178,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -430,12 +467,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="10.08984375" customWidth="1"/>
     <col min="3" max="3" width="9.54296875" customWidth="1"/>
-    <col min="4" max="4" width="9.90625" customWidth="1"/>
+    <col min="4" max="4" width="12.90625" customWidth="1"/>
+    <col min="5" max="5" width="23.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
@@ -455,6 +493,23 @@
         <v>4</v>
       </c>
     </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" t="s">
+        <v>27</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -462,8 +517,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{184529C9-730E-435E-BEE1-F0658F84F4E5}">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="3" max="3" width="15.54296875" customWidth="1"/>
+    <col min="4" max="4" width="17.08984375" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
@@ -482,6 +541,23 @@
         <v>0</v>
       </c>
     </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -489,8 +565,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC0A02D9-2E45-4C71-8D25-476171EB84F3}">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.26953125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
@@ -499,14 +579,31 @@
       <c r="B1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="6" t="s">
         <v>12</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="5">
+        <v>46128</v>
+      </c>
+      <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2">
+        <v>30</v>
+      </c>
+      <c r="E2" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -516,10 +613,11 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{316C30BC-E0B1-44D0-A87F-D6877B8147F3}">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.90625" customWidth="1"/>
+    <col min="6" max="6" width="9.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
@@ -542,6 +640,26 @@
         <v>10</v>
       </c>
     </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" s="7">
+        <v>25</v>
+      </c>
+      <c r="E2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" s="5">
+        <v>46128</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -549,7 +667,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75B16DBB-556A-43C0-AF68-1868EBDC800A}">
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.90625" customWidth="1"/>
@@ -566,6 +684,17 @@
         <v>5</v>
       </c>
     </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
